--- a/Part I SAAM Project - GROUP AT.xlsx
+++ b/Part I SAAM Project - GROUP AT.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/luigidimonte/GROUP-AT/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC77774F-CFED-304E-8449-14E90280760B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D891D0E-D881-2240-8AE5-079613BE04EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-29400" yWindow="660" windowWidth="29400" windowHeight="18460" xr2:uid="{769752CF-73B8-EF48-A8F0-90A2A5F36716}"/>
+    <workbookView xWindow="-29420" yWindow="660" windowWidth="29400" windowHeight="18460" xr2:uid="{769752CF-73B8-EF48-A8F0-90A2A5F36716}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
